--- a/data/trans_dic/IP07_C15_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C15_2023-Clase-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio (tasa de respuesta: 92,89%)</t>
+          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio/instituto (tasa de respuesta: 92,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 28,42</t>
+          <t>1,5; 12,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 14,91</t>
+          <t>4,95; 26,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 16,85</t>
+          <t>4,92; 17,04</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,31</t>
+          <t>2,91; 24,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 25,81</t>
+          <t>0,0; 21,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 17,38</t>
+          <t>3,45; 18,67</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,98</t>
+          <t>0,0; 15,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,76</t>
+          <t>0,0; 29,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 16,6</t>
+          <t>1,61; 16,89</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 26,0</t>
+          <t>5,03; 22,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,8; 23,97</t>
+          <t>10,36; 32,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 19,76</t>
+          <t>9,28; 23,27</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 20,31</t>
+          <t>3,3; 19,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 22,35</t>
+          <t>3,51; 17,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 17,55</t>
+          <t>4,59; 16,73</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,1; 24,98</t>
+          <t>5,9; 26,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,05; 29,3</t>
+          <t>2,14; 25,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,91; 21,8</t>
+          <t>5,95; 20,37</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,84; 14,68</t>
+          <t>6,61; 14,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,92; 14,61</t>
+          <t>8,06; 16,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,59; 13,67</t>
+          <t>7,98; 13,58</t>
         </is>
       </c>
     </row>
@@ -927,18 +927,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio (tasa de respuesta: 92,89%)</t>
+          <t>Menores que refieren que se han producido situaciones de cyberbulling fuera de su colegio/instituto (tasa de respuesta: 92,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5639</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1387; 8099</t>
+          <t>498; 4274</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>539; 4823</t>
+          <t>1475; 8006</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3015; 10256</t>
+          <t>3104; 10750</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>5275</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5960</t>
+          <t>894; 7507</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>945; 7737</t>
+          <t>0; 6383</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1877; 10068</t>
+          <t>2080; 11258</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2666</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4513</t>
+          <t>0; 4055</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4525</t>
+          <t>0; 4437</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>801; 6754</t>
+          <t>662; 6953</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7740</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15382</t>
+          <t>14969</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1647; 16798</t>
+          <t>3140; 14063</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3714; 15342</t>
+          <t>4242; 13462</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7583; 25410</t>
+          <t>9589; 24049</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>8745</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1219; 6721</t>
+          <t>1872; 11279</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1946; 13054</t>
+          <t>1271; 6511</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4372; 16061</t>
+          <t>4262; 15549</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>7735</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>859; 6926</t>
+          <t>2000; 9125</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2352; 9775</t>
+          <t>654; 7693</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4218; 13318</t>
+          <t>3835; 13127</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>20521</t>
+          <t>23851</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>25449</t>
+          <t>21178</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45970</t>
+          <t>45029</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11421; 28701</t>
+          <t>16099; 34093</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>16951; 35816</t>
+          <t>14658; 29232</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33458; 60263</t>
+          <t>33956; 57774</t>
         </is>
       </c>
     </row>
